--- a/Data/EC/NIT-9020154928.xlsx
+++ b/Data/EC/NIT-9020154928.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75E451AF-AAC0-4C5D-8265-D9B53DCF4ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{98C39F71-8DEF-47E2-9551-3DDF5972A95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{AA38147D-EA6B-459F-9D38-A63B702AFDF1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A9DA116C-2174-4602-84C2-EAAFB3513DEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="186">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -227,6 +227,12 @@
     <t>KEVIN ANDRES RODRIGUEZ BRAVO</t>
   </si>
   <si>
+    <t>2604</t>
+  </si>
+  <si>
+    <t>2603</t>
+  </si>
+  <si>
     <t>1007275817</t>
   </si>
   <si>
@@ -323,10 +329,7 @@
     <t>YAIR JOSE ROJAS CARDOZO</t>
   </si>
   <si>
-    <t>2604</t>
-  </si>
-  <si>
-    <t>2603</t>
+    <t>2602</t>
   </si>
   <si>
     <t>1052704036</t>
@@ -381,6 +384,12 @@
   </si>
   <si>
     <t>JUAN CARLOS HERNANDEZ DIAZ</t>
+  </si>
+  <si>
+    <t>2601</t>
+  </si>
+  <si>
+    <t>2512</t>
   </si>
   <si>
     <t>1074717196</t>
@@ -953,22 +962,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4567607-5C31-6FE3-96BB-EF9BB6AD2D07}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2B0330A-080F-63D8-0D83-6F4B0B73BFC6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -977,7 +986,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -990,7 +999,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1319,27 +1328,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F141573-47DD-4604-85BA-B755BD369AFE}">
-  <dimension ref="B2:J105"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17D61F63-0628-44B4-9415-60B187D6BC6E}">
+  <dimension ref="B2:J112"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.53125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -1348,7 +1357,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1359,7 +1368,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1370,7 +1379,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1381,10 +1390,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1397,8 +1406,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1413,15 +1422,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>5973071</v>
+        <v>6435315</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1429,27 +1438,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C13" s="5">
         <v>79</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F13" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1469,16 +1478,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1501,7 +1510,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1524,7 +1533,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1547,7 +1556,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1570,7 +1579,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1593,7 +1602,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1616,7 +1625,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1639,7 +1648,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1662,7 +1671,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1685,7 +1694,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1708,7 +1717,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1731,7 +1740,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1754,7 +1763,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1777,7 +1786,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1800,7 +1809,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1823,7 +1832,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1846,7 +1855,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1869,7 +1878,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1892,7 +1901,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1915,7 +1924,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1938,7 +1947,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1961,7 +1970,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1984,7 +1993,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -2007,7 +2016,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -2030,7 +2039,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -2053,7 +2062,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -2076,18 +2085,18 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E42" s="16" t="s">
         <v>62</v>
-      </c>
-      <c r="D42" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E42" s="16" t="s">
-        <v>11</v>
       </c>
       <c r="F42" s="18">
         <v>70037</v>
@@ -2099,18 +2108,18 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="F43" s="18">
         <v>70037</v>
@@ -2122,15 +2131,15 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E44" s="16" t="s">
         <v>11</v>
@@ -2145,15 +2154,15 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E45" s="16" t="s">
         <v>11</v>
@@ -2168,15 +2177,15 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E46" s="16" t="s">
         <v>11</v>
@@ -2191,15 +2200,15 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E47" s="16" t="s">
         <v>11</v>
@@ -2214,15 +2223,15 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E48" s="16" t="s">
         <v>11</v>
@@ -2237,15 +2246,15 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E49" s="16" t="s">
         <v>11</v>
@@ -2260,15 +2269,15 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E50" s="16" t="s">
         <v>11</v>
@@ -2283,15 +2292,15 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E51" s="16" t="s">
         <v>11</v>
@@ -2306,15 +2315,15 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E52" s="16" t="s">
         <v>11</v>
@@ -2329,15 +2338,15 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E53" s="16" t="s">
         <v>11</v>
@@ -2352,15 +2361,15 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E54" s="16" t="s">
         <v>11</v>
@@ -2375,15 +2384,15 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E55" s="16" t="s">
         <v>11</v>
@@ -2398,15 +2407,15 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E56" s="16" t="s">
         <v>11</v>
@@ -2421,18 +2430,18 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="F57" s="18">
         <v>70037</v>
@@ -2444,7 +2453,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2455,7 +2464,7 @@
         <v>93</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="F58" s="18">
         <v>70037</v>
@@ -2467,18 +2476,18 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F59" s="18">
         <v>70037</v>
@@ -2490,18 +2499,18 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="F60" s="18">
         <v>70037</v>
@@ -2513,18 +2522,18 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="F61" s="18">
         <v>70037</v>
@@ -2536,15 +2545,15 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E62" s="16" t="s">
         <v>11</v>
@@ -2559,15 +2568,15 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E63" s="16" t="s">
         <v>11</v>
@@ -2582,15 +2591,15 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E64" s="16" t="s">
         <v>11</v>
@@ -2605,15 +2614,15 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E65" s="16" t="s">
         <v>11</v>
@@ -2628,15 +2637,15 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E66" s="16" t="s">
         <v>11</v>
@@ -2651,38 +2660,38 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E67" s="16" t="s">
         <v>11</v>
       </c>
       <c r="F67" s="18">
-        <v>160000</v>
+        <v>70037</v>
       </c>
       <c r="G67" s="18">
-        <v>4000000</v>
+        <v>1750905</v>
       </c>
       <c r="H67" s="19"/>
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E68" s="16" t="s">
         <v>11</v>
@@ -2697,15 +2706,15 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D69" s="17" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E69" s="16" t="s">
         <v>11</v>
@@ -2720,41 +2729,41 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E70" s="16" t="s">
         <v>11</v>
       </c>
       <c r="F70" s="18">
-        <v>70037</v>
+        <v>160000</v>
       </c>
       <c r="G70" s="18">
-        <v>1750905</v>
+        <v>4000000</v>
       </c>
       <c r="H70" s="19"/>
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>11</v>
+        <v>115</v>
       </c>
       <c r="F71" s="18">
         <v>70037</v>
@@ -2766,21 +2775,21 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C72" s="16" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>11</v>
+        <v>116</v>
       </c>
       <c r="F72" s="18">
-        <v>70037</v>
+        <v>42022</v>
       </c>
       <c r="G72" s="18">
         <v>1750905</v>
@@ -2789,15 +2798,15 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C73" s="16" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E73" s="16" t="s">
         <v>11</v>
@@ -2812,15 +2821,15 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E74" s="16" t="s">
         <v>11</v>
@@ -2835,15 +2844,15 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E75" s="16" t="s">
         <v>11</v>
@@ -2858,15 +2867,15 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C76" s="16" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E76" s="16" t="s">
         <v>11</v>
@@ -2881,15 +2890,15 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C77" s="16" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="E77" s="16" t="s">
         <v>11</v>
@@ -2904,15 +2913,15 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E78" s="16" t="s">
         <v>11</v>
@@ -2927,15 +2936,15 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E79" s="16" t="s">
         <v>11</v>
@@ -2950,15 +2959,15 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E80" s="16" t="s">
         <v>11</v>
@@ -2973,15 +2982,15 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C81" s="16" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E81" s="16" t="s">
         <v>11</v>
@@ -2996,15 +3005,15 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E82" s="16" t="s">
         <v>11</v>
@@ -3019,15 +3028,15 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C83" s="16" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D83" s="17" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E83" s="16" t="s">
         <v>11</v>
@@ -3042,15 +3051,15 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C84" s="16" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D84" s="17" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E84" s="16" t="s">
         <v>11</v>
@@ -3065,15 +3074,15 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C85" s="16" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D85" s="17" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E85" s="16" t="s">
         <v>11</v>
@@ -3088,18 +3097,18 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>150</v>
+        <v>11</v>
       </c>
       <c r="F86" s="18">
         <v>70037</v>
@@ -3111,18 +3120,18 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C87" s="16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D87" s="17" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="F87" s="18">
         <v>70037</v>
@@ -3134,18 +3143,18 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C88" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D88" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="D88" s="17" t="s">
-        <v>149</v>
-      </c>
       <c r="E88" s="16" t="s">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="F88" s="18">
         <v>70037</v>
@@ -3157,18 +3166,18 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C89" s="16" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D89" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E89" s="16" t="s">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="F89" s="18">
         <v>70037</v>
@@ -3180,7 +3189,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -3191,7 +3200,7 @@
         <v>152</v>
       </c>
       <c r="E90" s="16" t="s">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="F90" s="18">
         <v>70037</v>
@@ -3203,18 +3212,18 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C91" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="D91" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="E91" s="16" t="s">
         <v>153</v>
-      </c>
-      <c r="D91" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="E91" s="16" t="s">
-        <v>11</v>
       </c>
       <c r="F91" s="18">
         <v>70037</v>
@@ -3226,18 +3235,18 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C92" s="16" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E92" s="16" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F92" s="18">
         <v>70037</v>
@@ -3249,18 +3258,18 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C93" s="16" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E93" s="16" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="F93" s="18">
         <v>70037</v>
@@ -3272,18 +3281,18 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C94" s="16" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E94" s="16" t="s">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="F94" s="18">
         <v>70037</v>
@@ -3295,18 +3304,18 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C95" s="16" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E95" s="16" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F95" s="18">
         <v>70037</v>
@@ -3318,18 +3327,18 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C96" s="16" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="E96" s="16" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="F96" s="18">
         <v>70037</v>
@@ -3341,18 +3350,18 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C97" s="16" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="D97" s="17" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E97" s="16" t="s">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="F97" s="18">
         <v>70037</v>
@@ -3364,15 +3373,15 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C98" s="16" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="D98" s="17" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="E98" s="16" t="s">
         <v>11</v>
@@ -3387,57 +3396,218 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B99" s="21" t="s">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B99" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C99" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D99" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="E99" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F99" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G99" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H99" s="19"/>
+      <c r="I99" s="19"/>
+      <c r="J99" s="20"/>
+    </row>
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B100" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C100" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D100" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="E100" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F100" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G100" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H100" s="19"/>
+      <c r="I100" s="19"/>
+      <c r="J100" s="20"/>
+    </row>
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B101" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C101" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="D101" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="E101" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G101" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H101" s="19"/>
+      <c r="I101" s="19"/>
+      <c r="J101" s="20"/>
+    </row>
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B102" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C102" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="D102" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="E102" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F102" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G102" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H102" s="19"/>
+      <c r="I102" s="19"/>
+      <c r="J102" s="20"/>
+    </row>
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B103" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C103" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D103" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="E103" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F103" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G103" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H103" s="19"/>
+      <c r="I103" s="19"/>
+      <c r="J103" s="20"/>
+    </row>
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B104" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C104" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="D104" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="C99" s="22" t="s">
+      <c r="E104" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F104" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G104" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H104" s="19"/>
+      <c r="I104" s="19"/>
+      <c r="J104" s="20"/>
+    </row>
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B105" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C105" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="D99" s="23" t="s">
+      <c r="D105" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="E99" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F99" s="24">
-        <v>70037</v>
-      </c>
-      <c r="G99" s="24">
-        <v>1750905</v>
-      </c>
-      <c r="H99" s="25"/>
-      <c r="I99" s="25"/>
-      <c r="J99" s="26"/>
-    </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B104" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="C104" s="32"/>
-      <c r="H104" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="I104" s="1"/>
-      <c r="J104" s="1"/>
-    </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B105" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="C105" s="32"/>
-      <c r="H105" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="I105" s="1"/>
-      <c r="J105" s="1"/>
+      <c r="E105" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F105" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G105" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H105" s="19"/>
+      <c r="I105" s="19"/>
+      <c r="J105" s="20"/>
+    </row>
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B106" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="C106" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="D106" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="E106" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F106" s="24">
+        <v>70037</v>
+      </c>
+      <c r="G106" s="24">
+        <v>1750905</v>
+      </c>
+      <c r="H106" s="25"/>
+      <c r="I106" s="25"/>
+      <c r="J106" s="26"/>
+    </row>
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B111" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="C111" s="32"/>
+      <c r="H111" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1"/>
+    </row>
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B112" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="C112" s="32"/>
+      <c r="H112" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="H105:J105"/>
-    <mergeCell ref="H104:J104"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="H112:J112"/>
+    <mergeCell ref="H111:J111"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
